--- a/artfynd/A 30272-2023 artfynd.xlsx
+++ b/artfynd/A 30272-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 30272-2023 artfynd.xlsx
+++ b/artfynd/A 30272-2023 artfynd.xlsx
@@ -2153,7 +2153,7 @@
         <v>111065267</v>
       </c>
       <c r="B15" t="n">
-        <v>5113</v>
+        <v>5166</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2190,10 +2190,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>618455.2067688531</v>
+        <v>618455</v>
       </c>
       <c r="R15" t="n">
-        <v>6904843.365927762</v>
+        <v>6904843</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2223,19 +2223,9 @@
           <t>2023-07-24</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2023-07-24</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 30272-2023 artfynd.xlsx
+++ b/artfynd/A 30272-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>111065265</v>
+        <v>111065266</v>
       </c>
       <c r="B2" t="n">
-        <v>89405</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>618433.1409164476</v>
+        <v>618434</v>
       </c>
       <c r="R2" t="n">
-        <v>6904846.784246631</v>
+        <v>6904845</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -748,19 +743,9 @@
           <t>2023-07-24</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-07-24</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,37 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111065388</v>
+        <v>112178654</v>
       </c>
       <c r="B3" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>618347.5686540804</v>
+        <v>618387</v>
       </c>
       <c r="R3" t="n">
-        <v>6904969.651671612</v>
+        <v>6904851</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -857,27 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-07-24</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-07-24</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>10 bladrosetter</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,37 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>111065383</v>
+        <v>111065265</v>
       </c>
       <c r="B4" t="n">
-        <v>5135</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>105930</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -944,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>618397.5114801975</v>
+        <v>618433</v>
       </c>
       <c r="R4" t="n">
-        <v>6904837.602457394</v>
+        <v>6904847</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -977,19 +937,9 @@
           <t>2023-07-24</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-07-24</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,37 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>111065399</v>
+        <v>111065392</v>
       </c>
       <c r="B5" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1056,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>618454.6357668397</v>
+        <v>618436</v>
       </c>
       <c r="R5" t="n">
-        <v>6904899.2943499</v>
+        <v>6904890</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1089,19 +1034,9 @@
           <t>2023-07-24</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-07-24</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>111065266</v>
+        <v>111065408</v>
       </c>
       <c r="B6" t="n">
-        <v>89686</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1144,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1168,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>618434.1392573146</v>
+        <v>618498</v>
       </c>
       <c r="R6" t="n">
-        <v>6904844.95447165</v>
+        <v>6904995</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1201,19 +1131,9 @@
           <t>2023-07-24</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-07-24</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,37 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>111065381</v>
+        <v>111065377</v>
       </c>
       <c r="B7" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96437</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>2667</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1280,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>618448.8786219922</v>
+        <v>618476</v>
       </c>
       <c r="R7" t="n">
-        <v>6904877.178313724</v>
+        <v>6904840</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1313,19 +1228,9 @@
           <t>2023-07-24</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-07-24</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1352,54 +1257,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>111065260</v>
+        <v>111065268</v>
       </c>
       <c r="B8" t="n">
-        <v>55611</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96441</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102612</v>
+        <v>2668</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Källåsen, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>618431.2330682677</v>
+        <v>618468</v>
       </c>
       <c r="R8" t="n">
-        <v>6904861.170441245</v>
+        <v>6904851</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1429,24 +1325,9 @@
           <t>2023-07-24</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-07-24</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>höna med 3 kycklingar</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1473,37 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>111065401</v>
+        <v>111065376</v>
       </c>
       <c r="B9" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>2671</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1513,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>618436.9486579391</v>
+        <v>618468</v>
       </c>
       <c r="R9" t="n">
-        <v>6904963.9429572</v>
+        <v>6904846</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1546,19 +1422,9 @@
           <t>2023-07-24</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-07-24</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1585,37 +1451,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>111065392</v>
+        <v>111065379</v>
       </c>
       <c r="B10" t="n">
-        <v>89405</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96231</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>2779</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1625,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>618436.7605589621</v>
+        <v>618473</v>
       </c>
       <c r="R10" t="n">
-        <v>6904889.805744221</v>
+        <v>6904851</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1658,27 +1519,18 @@
           <t>2023-07-24</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-07-24</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1700,12 +1552,7 @@
         <v>111065394</v>
       </c>
       <c r="B11" t="n">
-        <v>93057</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1737,10 +1584,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>618422.5078606633</v>
+        <v>618423</v>
       </c>
       <c r="R11" t="n">
-        <v>6904896.763121969</v>
+        <v>6904897</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1770,19 +1617,9 @@
           <t>2023-07-24</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2023-07-24</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1809,37 +1646,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>111065402</v>
+        <v>112178652</v>
       </c>
       <c r="B12" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>4366</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1849,10 +1681,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>618476.5337852607</v>
+        <v>618476</v>
       </c>
       <c r="R12" t="n">
-        <v>6905059.514784307</v>
+        <v>6905001</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1879,27 +1711,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-07-24</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-07-24</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>100 bladrosetter</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1926,37 +1743,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>111065385</v>
+        <v>112178651</v>
       </c>
       <c r="B13" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89156</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>4412</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1966,10 +1778,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>618318.5313652124</v>
+        <v>618388</v>
       </c>
       <c r="R13" t="n">
-        <v>6904892.633771772</v>
+        <v>6904949</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1996,22 +1808,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-07-24</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-07-24</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2038,37 +1840,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>111065387</v>
+        <v>111065397</v>
       </c>
       <c r="B14" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2078,10 +1875,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>618350.7085517345</v>
+        <v>618456</v>
       </c>
       <c r="R14" t="n">
-        <v>6904893.767037258</v>
+        <v>6904827</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2111,19 +1908,9 @@
           <t>2023-07-24</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2023-07-24</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2153,12 +1940,7 @@
         <v>111065267</v>
       </c>
       <c r="B15" t="n">
-        <v>5166</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2252,15 +2034,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>112178652</v>
+        <v>111065260</v>
       </c>
       <c r="B16" t="n">
-        <v>90865</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57132</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2268,34 +2045,38 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4366</v>
+        <v>102612</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Källåsen, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>618476</v>
+        <v>618431</v>
       </c>
       <c r="R16" t="n">
-        <v>6905002</v>
+        <v>6904861</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2322,12 +2103,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2023-07-24</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2023-07-24</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>höna med 3 kycklingar</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2354,37 +2140,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>112178651</v>
+        <v>111065383</v>
       </c>
       <c r="B17" t="n">
-        <v>86410</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4412</v>
+        <v>105930</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2394,10 +2175,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>618388</v>
+        <v>618398</v>
       </c>
       <c r="R17" t="n">
-        <v>6904949</v>
+        <v>6904837</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2424,12 +2205,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2023-07-24</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2023-07-24</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2456,37 +2237,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>112178654</v>
+        <v>111065381</v>
       </c>
       <c r="B18" t="n">
-        <v>89873</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2496,10 +2272,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>618387</v>
+        <v>618449</v>
       </c>
       <c r="R18" t="n">
-        <v>6904851</v>
+        <v>6904878</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2526,12 +2302,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2023-07-24</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2023-07-24</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2555,6 +2331,598 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>111065385</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Källåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>618319</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6904892</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2023-07-24</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2023-07-24</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>111065387</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Källåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>618351</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6904894</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2023-07-24</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2023-07-24</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>111065388</v>
+      </c>
+      <c r="B21" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Källåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>618348</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6904970</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2023-07-24</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2023-07-24</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>10 bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>111065399</v>
+      </c>
+      <c r="B22" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Källåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>618455</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6904899</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2023-07-24</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2023-07-24</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>111065401</v>
+      </c>
+      <c r="B23" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Källåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>618436</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6904964</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2023-07-24</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2023-07-24</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>111065402</v>
+      </c>
+      <c r="B24" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Källåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>618477</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6905060</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2023-07-24</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2023-07-24</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>100 bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 30272-2023 artfynd.xlsx
+++ b/artfynd/A 30272-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111065266</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112178654</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111065265</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111065392</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111065408</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111065377</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111065268</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111065376</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1546,6 +1591,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111065379</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1643,6 +1693,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111065394</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1740,6 +1795,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112178652</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1837,6 +1897,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112178651</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1934,6 +1999,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111065397</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2031,6 +2101,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111065267</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2137,6 +2212,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111065260</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2234,6 +2314,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111065383</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2331,6 +2416,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111065381</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2428,6 +2518,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111065385</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2525,6 +2620,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111065387</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2627,6 +2727,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111065388</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2724,6 +2829,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111065399</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2821,6 +2931,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111065401</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2923,8 +3038,38 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111065402</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>